--- a/v5_data/latest/market_review.xlsx
+++ b/v5_data/latest/market_review.xlsx
@@ -27731,7 +27731,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27741,40 +27741,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sina+eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>sina</t>
-        </is>
-      </c>
+          <t>legulegu_fallback+legulegu_limit_fallback</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>5557</v>
+        <v>5207</v>
       </c>
       <c r="G2" t="n">
-        <v>3166</v>
+        <v>3039</v>
       </c>
       <c r="H2" t="n">
-        <v>2196</v>
+        <v>1987</v>
       </c>
       <c r="I2" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="J2" t="n">
         <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5697318697138744</v>
+        <v>0.5836374111772614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3951772539139823</v>
+        <v>0.3816016900326484</v>
       </c>
       <c r="M2" t="n">
-        <v>970</v>
+        <v>1052</v>
       </c>
       <c r="N2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -27783,14 +27779,12 @@
         <v>19</v>
       </c>
       <c r="Q2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8303571428571429</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
+        <v>0.831858407079646</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>39</v>
       </c>
@@ -27809,11 +27803,7 @@
       <c r="Y2" t="b">
         <v>1</v>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>000428|000735|000759|000798|000816|000823|000978|001229|001267|001296|001330|001366|001389|002011|002138|002172|002281|002290|002403|002436|002463|002470|002483|002484|002515|002564|002579|002702|002708|002815|002852|002881|002902|002909|002916|002957|002963|002972|002975|002980|002988|300112|301516|301550|600103|600108|600127|600280|600330|600345|600354|600371|600400|600540|600770|600785|600791|600857|600865|601086|601595|601949|603009|603042|603083|603118|603119|603124|603186|603192|603228|603286|603311|603355|603395|603608|603626|603628|603668|603679|603696|603823|603826|603926|603936|603999|605168|605488|605577|688001|688655|688813|920821</t>
-        </is>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>002674|600076</t>
@@ -27835,10 +27825,10 @@
         </is>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>90</v>
@@ -27872,22 +27862,16 @@
       <c r="AP2" t="n">
         <v>2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>456</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1963772933937</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
           <t>上涨/下跌/平盘由逐股快照计数；涨停/跌停读取东方财富公开池；炸板、封板率、昨日涨停溢价、连板高度为影子情绪层，仅记录和QA，暂不改变推荐。乐咕只做交叉核验。</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AV2" t="n">
         <v>2</v>
@@ -27904,7 +27888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F358"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27947,17 +27931,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>000428</t>
+          <t>002674</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -27979,17 +27963,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>000735</t>
+          <t>600076</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -28011,17 +27995,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>000759</t>
+          <t>000523</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -28043,17 +28027,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>000798</t>
+          <t>000813</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -28075,17 +28059,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>000816</t>
+          <t>001210</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -28107,17 +28091,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>000823</t>
+          <t>002224</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -28139,17 +28123,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>000978</t>
+          <t>002516</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -28171,17 +28155,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>001229</t>
+          <t>002713</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -28203,17 +28187,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>001267</t>
+          <t>002885</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -28235,17 +28219,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>001296</t>
+          <t>300684</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -28267,17 +28251,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>001330</t>
+          <t>301529</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -28299,17 +28283,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>001366</t>
+          <t>301595</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -28331,17 +28315,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>001389</t>
+          <t>601118</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -28363,17 +28347,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>002011</t>
+          <t>603002</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -28395,17 +28379,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>002138</t>
+          <t>603011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -28427,17 +28411,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>002172</t>
+          <t>603030</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -28459,17 +28443,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>002281</t>
+          <t>603536</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -28491,17 +28475,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>002290</t>
+          <t>603773</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -28523,17 +28507,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>002403</t>
+          <t>605288</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -28555,17 +28539,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>002436</t>
+          <t>605580</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -28587,17 +28571,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>002463</t>
+          <t>688583</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -28619,17 +28603,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>002470</t>
+          <t>000428</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -28651,17 +28635,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>002483</t>
+          <t>000592</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -28683,17 +28667,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>002484</t>
+          <t>000702</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -28715,17 +28699,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>002515</t>
+          <t>000735</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -28747,17 +28731,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>002564</t>
+          <t>000798</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -28779,17 +28763,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>002579</t>
+          <t>000876</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -28811,17 +28795,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>002702</t>
+          <t>000892</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -28843,17 +28827,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>002708</t>
+          <t>001222</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -28875,17 +28859,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>002815</t>
+          <t>001316</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -28907,17 +28891,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>002852</t>
+          <t>001366</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -28939,17 +28923,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>002881</t>
+          <t>002124</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -28971,17 +28955,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>002902</t>
+          <t>002403</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -29003,17 +28987,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>002909</t>
+          <t>002564</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -29035,17 +29019,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>002916</t>
+          <t>002702</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -29067,17 +29051,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>002957</t>
+          <t>002827</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -29099,17 +29083,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>002963</t>
+          <t>002862</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -29131,17 +29115,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>002972</t>
+          <t>002868</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -29163,17 +29147,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>002975</t>
+          <t>002949</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -29195,17 +29179,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>002980</t>
+          <t>003040</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -29227,17 +29211,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>002988</t>
+          <t>600059</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -29259,17 +29243,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>300112</t>
+          <t>600108</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -29291,17 +29275,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>301516</t>
+          <t>600354</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -29323,17 +29307,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>301550</t>
+          <t>600506</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -29355,17 +29339,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>600103</t>
+          <t>600698</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -29387,17 +29371,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>600108</t>
+          <t>600802</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -29419,17 +29403,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>600127</t>
+          <t>600865</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -29451,17 +29435,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>600280</t>
+          <t>600975</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -29483,17 +29467,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>600330</t>
+          <t>601579</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -29515,17 +29499,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>600345</t>
+          <t>601949</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -29547,17 +29531,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>600354</t>
+          <t>603122</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -29579,17 +29563,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>600371</t>
+          <t>603123</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -29611,17 +29595,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>600400</t>
+          <t>603151</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -29643,17 +29627,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>600540</t>
+          <t>603162</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -29675,17 +29659,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>600770</t>
+          <t>603390</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -29707,17 +29691,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>600785</t>
+          <t>603696</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -29739,17 +29723,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>600791</t>
+          <t>605398</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -29771,17 +29755,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>600857</t>
+          <t>605577</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -29803,17 +29787,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>600865</t>
+          <t>605580</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -29835,17 +29819,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>昨日涨停</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>601086</t>
+          <t>920075</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -29867,17 +29851,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>601595</t>
+          <t>000017</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -29899,17 +29883,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>601949</t>
+          <t>000419</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -29931,17 +29915,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>603009</t>
+          <t>000428</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -29963,17 +29947,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>603042</t>
+          <t>000430</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -29995,17 +29979,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>603083</t>
+          <t>000501</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -30027,17 +30011,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>603118</t>
+          <t>000523</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -30059,17 +30043,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>603119</t>
+          <t>000560</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -30091,17 +30075,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>603124</t>
+          <t>000592</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -30123,17 +30107,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>603186</t>
+          <t>000626</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -30155,17 +30139,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>603192</t>
+          <t>000702</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -30187,17 +30171,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>603228</t>
+          <t>000715</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -30219,17 +30203,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>603286</t>
+          <t>000735</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -30251,17 +30235,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>603311</t>
+          <t>000755</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -30283,17 +30267,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>603355</t>
+          <t>000785</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -30315,17 +30299,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>603395</t>
+          <t>000798</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -30347,17 +30331,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>603608</t>
+          <t>000812</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -30379,17 +30363,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>603626</t>
+          <t>000813</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -30411,17 +30395,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>603628</t>
+          <t>000816</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -30443,17 +30427,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>603668</t>
+          <t>000822</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -30475,17 +30459,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>603679</t>
+          <t>000876</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -30507,17 +30491,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>603696</t>
+          <t>000892</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -30539,17 +30523,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>603823</t>
+          <t>000906</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -30571,17 +30555,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>603826</t>
+          <t>000930</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -30603,17 +30587,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>603926</t>
+          <t>000978</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -30635,17 +30619,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>603936</t>
+          <t>001201</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -30667,17 +30651,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>603999</t>
+          <t>001222</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -30699,17 +30683,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>605168</t>
+          <t>001228</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -30731,17 +30715,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>605488</t>
+          <t>001288</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -30763,17 +30747,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>605577</t>
+          <t>001330</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -30795,17 +30779,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>688001</t>
+          <t>001366</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -30827,17 +30811,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>688655</t>
+          <t>002011</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -30859,17 +30843,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>688813</t>
+          <t>002014</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -30891,17 +30875,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>920821</t>
+          <t>002059</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -30923,17 +30907,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>跌停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>002674</t>
+          <t>002062</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -30955,17 +30939,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>跌停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>600076</t>
+          <t>002069</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -30987,17 +30971,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>000523</t>
+          <t>002084</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -31019,17 +31003,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>000813</t>
+          <t>002086</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -31051,17 +31035,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>002100</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -31083,17 +31067,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>002224</t>
+          <t>002124</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -31115,17 +31099,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>002516</t>
+          <t>002187</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -31147,17 +31131,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>002713</t>
+          <t>002214</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -31179,17 +31163,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>002885</t>
+          <t>002215</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -31211,17 +31195,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>300684</t>
+          <t>002224</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -31243,17 +31227,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>301529</t>
+          <t>002234</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -31275,17 +31259,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>301595</t>
+          <t>002297</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -31307,17 +31291,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>601118</t>
+          <t>002300</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -31339,17 +31323,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>603002</t>
+          <t>002321</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -31371,17 +31355,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>603011</t>
+          <t>002403</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -31403,17 +31387,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>603030</t>
+          <t>002408</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -31435,17 +31419,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>603536</t>
+          <t>002419</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -31467,17 +31451,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>603773</t>
+          <t>002481</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -31499,17 +31483,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>605288</t>
+          <t>002548</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -31531,17 +31515,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>605580</t>
+          <t>002561</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -31563,17 +31547,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>688583</t>
+          <t>002564</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -31595,17 +31579,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>000428</t>
+          <t>002567</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -31627,17 +31611,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>000592</t>
+          <t>002602</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -31659,17 +31643,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>000702</t>
+          <t>002637</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -31691,17 +31675,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>000735</t>
+          <t>002702</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -31723,17 +31707,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>000798</t>
+          <t>002708</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -31755,17 +31739,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>000876</t>
+          <t>002746</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -31787,17 +31771,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>000892</t>
+          <t>002798</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -31819,17 +31803,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>001222</t>
+          <t>002827</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -31851,17 +31835,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>001316</t>
+          <t>002852</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -31883,17 +31867,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>001366</t>
+          <t>002855</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -31915,17 +31899,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>002124</t>
+          <t>002862</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -31947,17 +31931,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>002403</t>
+          <t>002881</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -31979,17 +31963,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>002564</t>
+          <t>002886</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -32011,17 +31995,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>002702</t>
+          <t>002909</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -32043,17 +32027,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>002827</t>
+          <t>002980</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -32075,17 +32059,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>002862</t>
+          <t>002982</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -32107,17 +32091,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>002868</t>
+          <t>002988</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -32139,17 +32123,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>002949</t>
+          <t>003005</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -32171,17 +32155,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>003040</t>
+          <t>003030</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -32203,17 +32187,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>600059</t>
+          <t>003040</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -32235,17 +32219,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>600108</t>
+          <t>300050</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -32267,17 +32251,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>600354</t>
+          <t>300094</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -32299,17 +32283,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>600506</t>
+          <t>300106</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -32331,17 +32315,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>600698</t>
+          <t>300189</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -32363,17 +32347,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>600802</t>
+          <t>300299</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -32395,17 +32379,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>600865</t>
+          <t>300300</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -32427,17 +32411,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>600975</t>
+          <t>300315</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -32459,17 +32443,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>601579</t>
+          <t>300350</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -32491,17 +32475,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>601949</t>
+          <t>300417</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -32523,17 +32507,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>603122</t>
+          <t>300428</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -32555,17 +32539,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>603123</t>
+          <t>300517</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -32587,17 +32571,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>603151</t>
+          <t>300559</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -32619,17 +32603,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>603162</t>
+          <t>300562</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -32651,17 +32635,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>603390</t>
+          <t>300684</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -32683,17 +32667,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>603696</t>
+          <t>300741</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -32715,17 +32699,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>605398</t>
+          <t>300778</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -32747,17 +32731,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>605577</t>
+          <t>300808</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -32779,17 +32763,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>605580</t>
+          <t>300829</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -32811,17 +32795,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>920075</t>
+          <t>300860</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -32843,7 +32827,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -32853,7 +32837,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>000017</t>
+          <t>300864</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -32875,7 +32859,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -32885,7 +32869,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>000419</t>
+          <t>300865</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -32907,7 +32891,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -32917,7 +32901,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>000428</t>
+          <t>300901</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -32939,7 +32923,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -32949,7 +32933,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>000430</t>
+          <t>300933</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -32971,7 +32955,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -32981,7 +32965,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>000501</t>
+          <t>300949</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -33003,7 +32987,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -33013,7 +32997,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>000523</t>
+          <t>300961</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -33035,7 +33019,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -33045,7 +33029,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>000560</t>
+          <t>300973</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -33067,7 +33051,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -33077,7 +33061,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>000592</t>
+          <t>300977</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -33099,7 +33083,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -33109,7 +33093,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>000626</t>
+          <t>301046</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -33131,7 +33115,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -33141,7 +33125,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>000702</t>
+          <t>301073</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -33163,7 +33147,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -33173,7 +33157,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>000715</t>
+          <t>301091</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -33195,7 +33179,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -33205,7 +33189,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>000735</t>
+          <t>301108</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -33227,7 +33211,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -33237,7 +33221,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>000755</t>
+          <t>301119</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -33259,7 +33243,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -33269,7 +33253,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>000785</t>
+          <t>301122</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -33291,7 +33275,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -33301,7 +33285,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>000798</t>
+          <t>301227</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -33323,7 +33307,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -33333,7 +33317,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>000812</t>
+          <t>301234</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -33355,7 +33339,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -33365,7 +33349,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>000813</t>
+          <t>301266</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -33387,7 +33371,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -33397,7 +33381,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>000816</t>
+          <t>301390</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -33419,7 +33403,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -33429,7 +33413,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>000822</t>
+          <t>301633</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -33451,7 +33435,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -33461,7 +33445,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>000876</t>
+          <t>600059</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -33483,7 +33467,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -33493,7 +33477,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>000892</t>
+          <t>600097</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -33515,7 +33499,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -33525,7 +33509,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>000906</t>
+          <t>600103</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -33547,7 +33531,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -33557,7 +33541,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>000930</t>
+          <t>600108</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -33579,7 +33563,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -33589,7 +33573,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>000978</t>
+          <t>600127</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -33611,7 +33595,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -33621,7 +33605,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>001201</t>
+          <t>600150</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -33643,7 +33627,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -33653,7 +33637,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>001222</t>
+          <t>600195</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -33675,7 +33659,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -33685,7 +33669,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>001228</t>
+          <t>600257</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -33707,7 +33691,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -33717,7 +33701,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>001288</t>
+          <t>600280</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -33739,7 +33723,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -33749,7 +33733,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>001330</t>
+          <t>600354</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -33771,7 +33755,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -33781,7 +33765,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>001366</t>
+          <t>600356</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -33803,7 +33787,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -33813,7 +33797,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>002011</t>
+          <t>600359</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -33835,7 +33819,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -33845,7 +33829,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>002014</t>
+          <t>600371</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -33867,7 +33851,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -33877,7 +33861,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>002059</t>
+          <t>600386</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -33899,7 +33883,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -33909,7 +33893,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>002062</t>
+          <t>600388</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -33931,7 +33915,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -33941,7 +33925,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>002069</t>
+          <t>600467</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -33963,7 +33947,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -33973,7 +33957,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>002084</t>
+          <t>600479</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -33995,7 +33979,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -34005,7 +33989,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>002086</t>
+          <t>600506</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -34027,7 +34011,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -34037,7 +34021,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>002100</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -34059,7 +34043,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -34069,7 +34053,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>002124</t>
+          <t>600628</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -34091,7 +34075,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -34101,7 +34085,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>002187</t>
+          <t>600629</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -34123,7 +34107,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -34133,7 +34117,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>002214</t>
+          <t>600657</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -34155,7 +34139,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -34165,7 +34149,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>002215</t>
+          <t>600689</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -34187,7 +34171,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -34197,7 +34181,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>002224</t>
+          <t>600697</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -34219,7 +34203,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -34229,7 +34213,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>002234</t>
+          <t>600698</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -34251,7 +34235,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -34261,7 +34245,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>002297</t>
+          <t>600737</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -34283,7 +34267,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -34293,7 +34277,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>002300</t>
+          <t>600738</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -34315,7 +34299,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -34325,7 +34309,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>002321</t>
+          <t>600774</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -34347,7 +34331,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -34357,7 +34341,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>002403</t>
+          <t>600801</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -34379,7 +34363,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -34389,7 +34373,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>002408</t>
+          <t>600802</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -34411,7 +34395,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -34421,7 +34405,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>002419</t>
+          <t>600803</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -34443,7 +34427,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -34453,7 +34437,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>002481</t>
+          <t>600814</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -34475,7 +34459,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -34485,7 +34469,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>002548</t>
+          <t>600822</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -34507,7 +34491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -34517,7 +34501,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>002561</t>
+          <t>600838</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -34539,7 +34523,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -34549,7 +34533,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>002564</t>
+          <t>600858</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -34571,7 +34555,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -34581,7 +34565,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>002567</t>
+          <t>600865</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -34603,7 +34587,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -34613,7 +34597,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>002602</t>
+          <t>600892</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -34635,7 +34619,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -34645,7 +34629,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>002637</t>
+          <t>600975</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -34667,7 +34651,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -34677,7 +34661,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>002702</t>
+          <t>601086</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -34699,7 +34683,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -34709,7 +34693,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>002708</t>
+          <t>601118</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -34731,7 +34715,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -34741,7 +34725,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>002746</t>
+          <t>601136</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -34763,7 +34747,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -34773,7 +34757,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>002798</t>
+          <t>601512</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -34795,7 +34779,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -34805,7 +34789,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>002827</t>
+          <t>601579</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -34827,7 +34811,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -34837,7 +34821,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>002852</t>
+          <t>601595</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -34859,7 +34843,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -34869,7 +34853,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>002855</t>
+          <t>601882</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -34891,7 +34875,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -34901,7 +34885,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>002862</t>
+          <t>601949</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -34923,7 +34907,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -34933,7 +34917,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>002881</t>
+          <t>601999</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -34955,7 +34939,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -34965,7 +34949,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>002886</t>
+          <t>603012</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -34987,7 +34971,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -34997,7 +34981,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>002909</t>
+          <t>603101</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -35019,7 +35003,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -35029,7 +35013,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>002980</t>
+          <t>603122</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -35051,7 +35035,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -35061,7 +35045,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>002982</t>
+          <t>603123</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -35083,7 +35067,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -35093,7 +35077,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>002988</t>
+          <t>603128</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -35115,7 +35099,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -35125,7 +35109,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>003005</t>
+          <t>603151</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -35147,7 +35131,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -35157,7 +35141,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>003030</t>
+          <t>603162</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -35179,7 +35163,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -35189,7 +35173,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>003040</t>
+          <t>603235</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -35211,7 +35195,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -35221,7 +35205,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>300050</t>
+          <t>603258</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -35243,7 +35227,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -35253,7 +35237,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>300094</t>
+          <t>603270</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -35275,7 +35259,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -35285,7 +35269,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>300106</t>
+          <t>603289</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -35307,7 +35291,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -35317,7 +35301,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>300189</t>
+          <t>603321</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -35339,7 +35323,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -35349,7 +35333,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>300299</t>
+          <t>603400</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -35371,7 +35355,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -35381,7 +35365,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>300300</t>
+          <t>603536</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -35403,7 +35387,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -35413,7 +35397,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>300315</t>
+          <t>603587</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -35435,7 +35419,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -35445,7 +35429,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>300350</t>
+          <t>603609</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -35467,7 +35451,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -35477,7 +35461,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>300417</t>
+          <t>603628</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -35499,7 +35483,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -35509,7 +35493,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>300428</t>
+          <t>603648</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -35531,7 +35515,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -35541,7 +35525,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>300517</t>
+          <t>603696</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -35563,7 +35547,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -35573,7 +35557,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>300559</t>
+          <t>603819</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -35595,7 +35579,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -35605,7 +35589,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>300562</t>
+          <t>603866</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -35627,7 +35611,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -35637,7 +35621,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>300684</t>
+          <t>603880</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -35659,7 +35643,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -35669,7 +35653,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>300741</t>
+          <t>603970</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -35691,7 +35675,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -35701,7 +35685,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>300778</t>
+          <t>603976</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -35723,7 +35707,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -35733,7 +35717,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>300808</t>
+          <t>603999</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -35755,7 +35739,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -35765,7 +35749,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>300829</t>
+          <t>605008</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -35787,7 +35771,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -35797,7 +35781,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>300860</t>
+          <t>605398</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -35819,7 +35803,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -35829,7 +35813,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>300864</t>
+          <t>605577</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -35851,7 +35835,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -35861,7 +35845,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>300865</t>
+          <t>605580</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -35883,7 +35867,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -35893,7 +35877,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>300901</t>
+          <t>688023</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -35915,7 +35899,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -35925,7 +35909,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>300933</t>
+          <t>688060</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -35947,7 +35931,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -35957,7 +35941,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>300949</t>
+          <t>688078</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -35979,7 +35963,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -35989,7 +35973,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>300961</t>
+          <t>688203</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -36011,7 +35995,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -36021,7 +36005,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>300973</t>
+          <t>688435</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -36043,7 +36027,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -36053,7 +36037,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>300977</t>
+          <t>688485</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -36075,7 +36059,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -36085,7 +36069,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>301046</t>
+          <t>688621</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -36107,7 +36091,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -36117,7 +36101,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>301073</t>
+          <t>688656</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -36139,7 +36123,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -36149,7 +36133,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>301091</t>
+          <t>688696</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -36171,7 +36155,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -36181,7 +36165,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>301108</t>
+          <t>920075</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -36203,7 +36187,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -36213,7 +36197,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>301119</t>
+          <t>920419</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -36235,7 +36219,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -36245,7 +36229,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>301122</t>
+          <t>920422</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -36267,7 +36251,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -36277,7 +36261,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>301227</t>
+          <t>920455</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -36299,7 +36283,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -36309,7 +36293,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>301234</t>
+          <t>920786</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -36331,7 +36315,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -36341,7 +36325,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>301266</t>
+          <t>920826</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -36363,7 +36347,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -36373,7 +36357,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>301390</t>
+          <t>920970</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -36382,2982 +36366,6 @@
         </is>
       </c>
       <c r="F265" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>301633</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>600059</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>600097</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>600103</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>600108</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>600127</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>600150</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>600195</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>600257</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>600280</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>600354</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>600356</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>600359</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>600371</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>600386</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>600388</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>600467</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>600479</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>600506</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>600540</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>600628</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>600629</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>600657</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>600689</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>600697</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>600698</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>600737</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>600738</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>600774</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>600801</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>600802</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>600803</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>600814</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>600822</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>600838</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>600858</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>600865</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>600892</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>600975</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>601086</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>601118</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>601136</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>601512</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>601579</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>601595</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>601882</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>601949</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>601999</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>603012</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>603101</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>603122</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>603123</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>603128</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>603151</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>603162</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>603235</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>603258</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>603270</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>603289</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>603321</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>603400</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>603536</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>603587</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>603609</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>603628</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>603648</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>603696</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>603819</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>603866</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>603880</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>603970</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>603976</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>603999</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>605008</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>605398</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>605577</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>605580</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>688023</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>688060</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>688078</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>688203</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>688435</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>688485</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>688621</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>688656</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>688696</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>920075</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>920419</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>920422</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>920455</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>920786</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>920826</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>2026-09-07 18:23:49+0800</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>920970</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
         <is>
           <t>第一阶段影子记录</t>
         </is>
@@ -39982,7 +36990,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07 18:23:49+0800</t>
+          <t>2026-09-07 20:37:23+0800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -39992,40 +37000,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sina+eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sina</t>
-        </is>
-      </c>
+          <t>legulegu_fallback+legulegu_limit_fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>5557</v>
+        <v>5207</v>
       </c>
       <c r="G4" t="n">
-        <v>3166</v>
+        <v>3039</v>
       </c>
       <c r="H4" t="n">
-        <v>2196</v>
+        <v>1987</v>
       </c>
       <c r="I4" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5697318697138744</v>
+        <v>0.5836374111772614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3951772539139823</v>
+        <v>0.3816016900326484</v>
       </c>
       <c r="M4" t="n">
-        <v>970</v>
+        <v>1052</v>
       </c>
       <c r="N4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
@@ -40034,14 +37038,12 @@
         <v>19</v>
       </c>
       <c r="Q4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8303571428571429</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
+        <v>0.831858407079646</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
         <v>39</v>
       </c>
@@ -40060,11 +37062,7 @@
       <c r="Y4" t="b">
         <v>1</v>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>000428|000735|000759|000798|000816|000823|000978|001229|001267|001296|001330|001366|001389|002011|002138|002172|002281|002290|002403|002436|002463|002470|002483|002484|002515|002564|002579|002702|002708|002815|002852|002881|002902|002909|002916|002957|002963|002972|002975|002980|002988|300112|301516|301550|600103|600108|600127|600280|600330|600345|600354|600371|600400|600540|600770|600785|600791|600857|600865|601086|601595|601949|603009|603042|603083|603118|603119|603124|603186|603192|603228|603286|603311|603355|603395|603608|603626|603628|603668|603679|603696|603823|603826|603926|603936|603999|605168|605488|605577|688001|688655|688813|920821</t>
-        </is>
-      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>002674|600076</t>
@@ -40086,10 +37084,10 @@
         </is>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="n">
         <v>90</v>
@@ -40123,22 +37121,16 @@
       <c r="AP4" t="n">
         <v>2</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>456</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1963772933937</v>
-      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
           <t>上涨/下跌/平盘由逐股快照计数；涨停/跌停读取东方财富公开池；炸板、封板率、昨日涨停溢价、连板高度为影子情绪层，仅记录和QA，暂不改变推荐。乐咕只做交叉核验。</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AV4" t="n">
         <v>2</v>
@@ -40160,7 +37152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40394,36 +37386,6 @@
           <t>成交额较前一日变化率</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>全市场成交额_5日均值</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>全市场成交额_5日分位</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>全市场成交额_20日均值</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>全市场成交额_20日分位</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>全市场成交额_60日均值</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>全市场成交额_60日分位</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40440,97 +37402,97 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5697318697138744</v>
+        <v>0.5836374111772614</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2339982963565386</v>
+        <v>0.2479038378199257</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4125528190383808</v>
+        <v>0.4171879995261765</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4125528190383808</v>
+        <v>0.4171879995261765</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4125528190383808</v>
+        <v>0.4171879995261765</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3951772539139823</v>
+        <v>0.3816016900326484</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2327255363650456</v>
+        <v>-0.2463011002463796</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5552866741956536</v>
+        <v>0.5507614862352089</v>
       </c>
       <c r="O2" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5552866741956536</v>
+        <v>0.5507614862352089</v>
       </c>
       <c r="Q2" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5552866741956536</v>
+        <v>0.5507614862352089</v>
       </c>
       <c r="S2" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="T2" t="n">
-        <v>970</v>
+        <v>1052</v>
       </c>
       <c r="U2" t="n">
-        <v>2593</v>
+        <v>2675</v>
       </c>
       <c r="V2" t="n">
-        <v>-792.6666666666666</v>
+        <v>-765.3333333333334</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-792.6666666666666</v>
+        <v>-765.3333333333334</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>-792.6666666666666</v>
+        <v>-765.3333333333334</v>
       </c>
       <c r="AA2" t="n">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AD2" t="n">
-        <v>59</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>59</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="AG2" t="n">
         <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>59</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="AI2" t="n">
         <v>1</v>
@@ -40560,31 +37522,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="AR2" t="n">
-        <v>1963772933937</v>
+        <v>1922241144323</v>
       </c>
       <c r="AS2" t="n">
-        <v>41531789614</v>
+        <v>142295022861</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.02160592063938327</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1888653399907.333</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1888653399907.333</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1888653399907.333</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1</v>
+        <v>0.07994344387465091</v>
       </c>
     </row>
   </sheetData>
@@ -40598,7 +37542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40794,7 +37738,7 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -40803,9 +37747,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ConnectionError:('Connection aborted.', ConnectionResetError(104, 'Connection reset by peer'))</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40930,7 +37878,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>失败</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -40939,65 +37887,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5557</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>有效涨跌幅=5557; 尝试次数=1</t>
+          <t>尝试次数=2; 第1次:ReadTimeout:HTTPConnectionPool(host='vip.stock.finance.sina.com.cn', port=80): Read timed out. (read timeout=None) | 第2次:ReadTimeout:HTTPConnectionPool(host='vip.stock.finance.sina.com.cn', port=80): Read timed out. (read timeout=None)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>全市场逐股快照正式源</t>
+          <t>正式口径与乐咕差异</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sina</t>
+          <t>legulegu_fallback+legulegu_limit_fallback</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5557</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>按有效涨跌幅覆盖数择优</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>正式口径与乐咕差异</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>警告</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>sina+eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>上涨:正式3166/乐咕3039 | 下跌:正式2196/乐咕1987 | 平盘:正式195/乐咕181 | 涨停:正式93/乐咕94</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/v5_data/latest/market_review.xlsx
+++ b/v5_data/latest/market_review.xlsx
@@ -27726,12 +27726,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27746,88 +27746,88 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>5206</v>
+        <v>5207</v>
       </c>
       <c r="G2" t="n">
-        <v>931</v>
+        <v>604</v>
       </c>
       <c r="H2" t="n">
-        <v>4192</v>
+        <v>4567</v>
       </c>
       <c r="I2" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
         <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1788321167883212</v>
+        <v>0.115997695410025</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8052247406838263</v>
+        <v>0.8770885346648742</v>
       </c>
       <c r="M2" t="n">
-        <v>-3261</v>
+        <v>-3963</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6140350877192983</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1044680929432313</v>
+        <v>0.5672386062996729</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4571428571428571</v>
       </c>
       <c r="W2" t="n">
-        <v>4.41719619252465</v>
+        <v>2.775486893124051</v>
       </c>
       <c r="X2" t="n">
-        <v>206</v>
+        <v>90</v>
       </c>
       <c r="Y2" t="b">
         <v>1</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>000636|000823|000980|000993|001232|002161|002201|002218|002242|002519|002560|002585|002790|002815|002848|002902|002912|300563|600088|600184|600207|600237|600410|600876|600967|601199|603136|603336|603386|603421|603439|603466|603693|603936|603938|605011|605058|605069|605088|605258</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>000017|000428|000523|000737|002040|002059|002162|002295|002403|002661|002702|002855|002909|600108|600318|600479|600540|600865|601949|603123|603366</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>000070|000679|000722|000759|000890|000978|002194|002297|003013|600255|600359|600371|600706|600712|600792|603226|603328|603601</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>000048|000532|000565|000722|000823|000978|000993|001299|002174|002201|002204|002377|002531|002543|002636|002661|002790|002912|600192|600318|600359|600488|600644|600667|600712|600744|600792|600876|601231|603105|603316|603318|603421|603601|920268</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>000017|000020|000912|002365|002855|003040|600479|600737|601118|603042|603090</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>000523|000759|000889|000930|000972|002040|002242|002295|002457|002552|002735|003029|301176|600403|600812|600844|601949|601999|603162|603366|605006|605177</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>000019|000523|000565|000759|000798|000912|000930|000972|000978|000980|000993|002040|002046|002068|002077|002155|002162|002295|002349|002377|002470|002498|002790|600121|600192|600255|600359|600403|600540|600698|600778|600792|600865|600869|601579|601872|601890|603042|603162|603186|603308|603328|603421|603650|603900|605077|605162|605198</t>
-        </is>
-      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>000096|000407|000507|000523|000550|000554|000558|000565|000731|000753|000759|000798|000803|000807|000823|000829|000886|000905|000912|000921|000930|000933|000968|000972|000978|000980|000993|001205|001209|001338|001368|002004|002011|002040|002068|002084|002142|002161|002162|002166|002172|002187|002204|002209|002246|002295|002320|002343|002349|002377|002389|002403|002408|002451|002470|002481|002493|002561|002579|002596|002616|002651|002652|002661|002692|002702|002790|002807|002909|002911|002913|002966|002980|003006|003029|300008|300013|300021|300050|300135|300154|300332|300335|300483|300589|300600|300673|300741|300788|300810|300951|301016|301046|301085|301223|301251|301282|301505|600017|600075|600104|600108|600121|600138|600150|600177|600192|600249|600256|600279|600303|600307|600318|600333|600336|600354|600359|600371|600403|600540|600681|600685|600704|600706|600710|600712|600731|600758|600764|600778|600792|600794|600802|600812|600822|600864|600865|600871|600874|600893|600903|600908|600917|600919|600926|600939|600989|601007|601008|601009|601015|601018|601022|601086|601107|601128|601188|601298|601326|601330|601528|601577|601579|601595|601665|601838|601866|601890|601949|601952|601969|601998|603042|603069|603103|603105|603136|603162|603186|603209|603216|603235|603268|603322|603323|603366|603393|603421|603518|603600|603619|603679|603689|603823|603900|603955|603967|603991|603999|605077|688215|688655|688656|688660|920010|920895</t>
+          <t>000523|000565|000722|000759|000798|000823|000839|000912|000921|000930|000978|000980|000993|001234|002011|002068|002161|002174|002201|002242|002265|002295|002316|002349|002377|002389|002403|002443|002470|002508|002652|002702|002790|002848|002909|002912|002913|002966|002998|003006|300183|300369|300411|300427|300741|301006|301357|600016|600088|600104|600108|600163|600177|600192|600310|600354|600359|600371|600540|600682|600706|600710|600712|600792|600865|600876|600919|600938|601009|601086|601330|601595|601838|601949|603042|603105|603136|603268|603421|603657|603938|605077|605177|688023|688151|688543|688581|688655|920008|920821</t>
         </is>
       </c>
       <c r="AE2" t="b">
@@ -27837,36 +27837,36 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-09-10 15:00:00</t>
+          <t>2026-09-11 15:00:00</t>
         </is>
       </c>
       <c r="AL2" t="n">
-        <v>931</v>
+        <v>604</v>
       </c>
       <c r="AM2" t="n">
-        <v>4192</v>
+        <v>4567</v>
       </c>
       <c r="AN2" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
@@ -27877,10 +27877,10 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -27894,7 +27894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F323"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27932,12 +27932,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27947,7 +27947,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>000048</t>
+          <t>000636</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -27964,12 +27964,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>000532</t>
+          <t>000823</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -27996,12 +27996,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -28011,7 +28011,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>000565</t>
+          <t>000980</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -28028,12 +28028,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>000722</t>
+          <t>000993</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -28060,12 +28060,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -28075,7 +28075,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>000823</t>
+          <t>001232</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -28092,12 +28092,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>000978</t>
+          <t>002161</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -28124,12 +28124,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>000993</t>
+          <t>002201</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -28156,12 +28156,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>001299</t>
+          <t>002218</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -28188,12 +28188,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -28203,7 +28203,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>002174</t>
+          <t>002242</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -28220,12 +28220,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -28235,7 +28235,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>002201</t>
+          <t>002519</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -28252,12 +28252,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -28267,7 +28267,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>002204</t>
+          <t>002560</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -28284,12 +28284,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -28299,7 +28299,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>002377</t>
+          <t>002585</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -28316,12 +28316,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -28331,7 +28331,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>002531</t>
+          <t>002790</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -28348,12 +28348,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>002543</t>
+          <t>002815</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -28380,12 +28380,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -28395,7 +28395,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>002636</t>
+          <t>002848</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -28412,12 +28412,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -28427,7 +28427,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>002661</t>
+          <t>002902</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -28444,12 +28444,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -28459,7 +28459,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>002790</t>
+          <t>002912</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -28476,12 +28476,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>002912</t>
+          <t>300563</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -28508,12 +28508,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>600192</t>
+          <t>600088</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -28540,12 +28540,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -28555,7 +28555,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>600318</t>
+          <t>600184</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -28572,12 +28572,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -28587,7 +28587,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>600359</t>
+          <t>600207</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -28604,12 +28604,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>600488</t>
+          <t>600237</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -28636,12 +28636,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -28651,7 +28651,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>600644</t>
+          <t>600410</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -28668,12 +28668,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -28683,7 +28683,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>600667</t>
+          <t>600876</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -28700,12 +28700,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -28715,7 +28715,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>600712</t>
+          <t>600967</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -28732,12 +28732,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -28747,7 +28747,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>600744</t>
+          <t>601199</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -28764,12 +28764,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>600792</t>
+          <t>603136</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -28796,12 +28796,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -28811,7 +28811,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>600876</t>
+          <t>603336</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -28828,12 +28828,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -28843,7 +28843,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>601231</t>
+          <t>603386</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -28860,12 +28860,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -28875,7 +28875,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>603105</t>
+          <t>603421</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -28892,12 +28892,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -28907,7 +28907,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>603316</t>
+          <t>603439</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -28924,12 +28924,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>603318</t>
+          <t>603466</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -28956,12 +28956,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -28971,7 +28971,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>603421</t>
+          <t>603693</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -28988,12 +28988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -29003,7 +29003,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>603601</t>
+          <t>603936</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -29020,12 +29020,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>920268</t>
+          <t>603938</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -29052,22 +29052,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>跌停</t>
+          <t>涨停</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>000017</t>
+          <t>605011</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -29084,22 +29084,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>跌停</t>
+          <t>涨停</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>000020</t>
+          <t>605058</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -29116,22 +29116,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>跌停</t>
+          <t>涨停</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>000912</t>
+          <t>605069</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -29148,22 +29148,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>跌停</t>
+          <t>涨停</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>002365</t>
+          <t>605088</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -29180,22 +29180,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>跌停</t>
+          <t>涨停</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>002855</t>
+          <t>605258</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -29212,12 +29212,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>003040</t>
+          <t>000017</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -29244,12 +29244,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>600479</t>
+          <t>000428</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -29276,12 +29276,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -29291,7 +29291,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>600737</t>
+          <t>000523</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -29308,12 +29308,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -29323,7 +29323,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>601118</t>
+          <t>000737</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -29340,12 +29340,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>603042</t>
+          <t>002040</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -29372,12 +29372,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -29387,7 +29387,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>603090</t>
+          <t>002059</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -29404,22 +29404,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>000523</t>
+          <t>002162</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -29436,22 +29436,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>000759</t>
+          <t>002295</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -29468,22 +29468,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>000889</t>
+          <t>002403</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -29500,22 +29500,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>000930</t>
+          <t>002661</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -29532,22 +29532,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>000972</t>
+          <t>002702</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -29564,22 +29564,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>002040</t>
+          <t>002855</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -29596,22 +29596,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>002242</t>
+          <t>002909</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -29628,22 +29628,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>002295</t>
+          <t>600108</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -29660,22 +29660,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>002457</t>
+          <t>600318</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -29692,22 +29692,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>002552</t>
+          <t>600479</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -29724,22 +29724,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>002735</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -29756,22 +29756,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>003029</t>
+          <t>600865</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -29788,22 +29788,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>301176</t>
+          <t>601949</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -29820,22 +29820,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>600403</t>
+          <t>603123</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -29852,22 +29852,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>炸板</t>
+          <t>跌停</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>600812</t>
+          <t>603366</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -29884,12 +29884,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -29899,7 +29899,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>600844</t>
+          <t>000070</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -29916,12 +29916,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -29931,7 +29931,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>601949</t>
+          <t>000679</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -29948,12 +29948,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -29963,7 +29963,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>601999</t>
+          <t>000722</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -29980,12 +29980,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>603162</t>
+          <t>000759</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -30012,12 +30012,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -30027,7 +30027,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>603366</t>
+          <t>000890</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -30044,12 +30044,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -30059,7 +30059,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>605006</t>
+          <t>000978</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -30076,12 +30076,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>605177</t>
+          <t>002194</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -30108,22 +30108,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>000019</t>
+          <t>002297</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -30140,22 +30140,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>000523</t>
+          <t>003013</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -30172,22 +30172,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>000565</t>
+          <t>600255</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -30204,22 +30204,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>000759</t>
+          <t>600359</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -30236,22 +30236,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>000798</t>
+          <t>600371</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -30268,22 +30268,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>000912</t>
+          <t>600706</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -30300,22 +30300,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>000930</t>
+          <t>600712</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -30332,22 +30332,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>000972</t>
+          <t>600792</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -30364,22 +30364,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>000978</t>
+          <t>603226</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -30396,22 +30396,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>000980</t>
+          <t>603328</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -30428,22 +30428,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>炸板</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>000993</t>
+          <t>603601</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -30460,12 +30460,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -30475,7 +30475,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>002040</t>
+          <t>000048</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -30492,12 +30492,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -30507,7 +30507,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>002046</t>
+          <t>000532</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -30524,12 +30524,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -30539,7 +30539,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>002068</t>
+          <t>000565</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -30556,12 +30556,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>002077</t>
+          <t>000722</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -30588,12 +30588,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -30603,7 +30603,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>002155</t>
+          <t>000823</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -30620,12 +30620,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -30635,7 +30635,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>002162</t>
+          <t>000978</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -30652,12 +30652,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -30667,7 +30667,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>002295</t>
+          <t>000993</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -30684,12 +30684,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -30699,7 +30699,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>002349</t>
+          <t>001299</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -30716,12 +30716,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>002377</t>
+          <t>002174</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -30748,12 +30748,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -30763,7 +30763,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>002470</t>
+          <t>002201</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -30780,12 +30780,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>002498</t>
+          <t>002204</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -30812,12 +30812,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -30827,7 +30827,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>002790</t>
+          <t>002377</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -30844,12 +30844,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -30859,7 +30859,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>600121</t>
+          <t>002531</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -30876,12 +30876,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -30891,7 +30891,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>600192</t>
+          <t>002543</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -30908,12 +30908,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -30923,7 +30923,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>600255</t>
+          <t>002636</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -30940,12 +30940,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -30955,7 +30955,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>600359</t>
+          <t>002661</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -30972,12 +30972,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -30987,7 +30987,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>600403</t>
+          <t>002790</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -31004,12 +31004,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>600540</t>
+          <t>002912</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -31036,12 +31036,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>600698</t>
+          <t>600192</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -31068,12 +31068,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -31083,7 +31083,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>600778</t>
+          <t>600318</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -31100,12 +31100,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -31115,7 +31115,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>600792</t>
+          <t>600359</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -31132,12 +31132,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>600865</t>
+          <t>600488</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -31164,12 +31164,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>600869</t>
+          <t>600644</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -31196,12 +31196,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -31211,7 +31211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>601579</t>
+          <t>600667</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -31228,12 +31228,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -31243,7 +31243,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>601872</t>
+          <t>600712</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -31260,12 +31260,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -31275,7 +31275,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>601890</t>
+          <t>600744</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -31292,12 +31292,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -31307,7 +31307,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>603042</t>
+          <t>600792</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -31324,12 +31324,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -31339,7 +31339,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>603162</t>
+          <t>600876</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -31356,12 +31356,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -31371,7 +31371,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>603186</t>
+          <t>601231</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -31388,12 +31388,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>603308</t>
+          <t>603105</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -31420,12 +31420,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -31435,7 +31435,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>603328</t>
+          <t>603316</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -31452,12 +31452,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -31467,7 +31467,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>603421</t>
+          <t>603318</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -31484,12 +31484,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -31499,7 +31499,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>603650</t>
+          <t>603421</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -31516,12 +31516,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -31531,7 +31531,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>603900</t>
+          <t>603601</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -31548,12 +31548,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>605077</t>
+          <t>920268</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -31580,22 +31580,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>605162</t>
+          <t>000523</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -31612,22 +31612,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>昨日涨停</t>
+          <t>强势股</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>605198</t>
+          <t>000565</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -31644,12 +31644,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>000096</t>
+          <t>000722</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -31676,12 +31676,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -31691,7 +31691,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>000407</t>
+          <t>000759</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -31708,12 +31708,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -31723,7 +31723,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>000507</t>
+          <t>000798</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -31740,12 +31740,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -31755,7 +31755,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>000523</t>
+          <t>000823</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -31772,12 +31772,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -31787,7 +31787,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>000550</t>
+          <t>000839</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -31804,12 +31804,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -31819,7 +31819,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>000554</t>
+          <t>000912</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -31836,12 +31836,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>000558</t>
+          <t>000921</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -31868,12 +31868,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -31883,7 +31883,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>000565</t>
+          <t>000930</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -31900,12 +31900,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -31915,7 +31915,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>000731</t>
+          <t>000978</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -31932,12 +31932,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -31947,7 +31947,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>000753</t>
+          <t>000980</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -31964,12 +31964,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -31979,7 +31979,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>000759</t>
+          <t>000993</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -31996,12 +31996,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -32011,7 +32011,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>000798</t>
+          <t>001234</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -32028,12 +32028,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -32043,7 +32043,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>000803</t>
+          <t>002011</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -32060,12 +32060,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -32075,7 +32075,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>000807</t>
+          <t>002068</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -32092,12 +32092,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -32107,7 +32107,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>000823</t>
+          <t>002161</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -32124,12 +32124,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -32139,7 +32139,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>000829</t>
+          <t>002174</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -32156,12 +32156,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -32171,7 +32171,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>000886</t>
+          <t>002201</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -32188,12 +32188,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -32203,7 +32203,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>000905</t>
+          <t>002242</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -32220,12 +32220,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -32235,7 +32235,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>000912</t>
+          <t>002265</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -32252,12 +32252,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -32267,7 +32267,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>000921</t>
+          <t>002295</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -32284,12 +32284,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -32299,7 +32299,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>000930</t>
+          <t>002316</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -32316,12 +32316,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -32331,7 +32331,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>000933</t>
+          <t>002349</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -32348,12 +32348,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -32363,7 +32363,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>000968</t>
+          <t>002377</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -32380,12 +32380,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>000972</t>
+          <t>002389</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -32412,12 +32412,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -32427,7 +32427,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>000978</t>
+          <t>002403</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -32444,12 +32444,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -32459,7 +32459,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>000980</t>
+          <t>002443</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -32476,12 +32476,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -32491,7 +32491,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>000993</t>
+          <t>002470</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -32508,12 +32508,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -32523,7 +32523,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>001205</t>
+          <t>002508</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -32540,12 +32540,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>001209</t>
+          <t>002652</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -32572,12 +32572,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -32587,7 +32587,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>001338</t>
+          <t>002702</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -32604,12 +32604,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -32619,7 +32619,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>001368</t>
+          <t>002790</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -32636,12 +32636,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -32651,7 +32651,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>002004</t>
+          <t>002848</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -32668,12 +32668,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>002011</t>
+          <t>002909</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -32700,12 +32700,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -32715,7 +32715,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>002040</t>
+          <t>002912</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -32732,12 +32732,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -32747,7 +32747,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>002068</t>
+          <t>002913</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -32764,12 +32764,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>002084</t>
+          <t>002966</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -32796,12 +32796,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>002142</t>
+          <t>002998</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -32828,12 +32828,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -32843,7 +32843,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>002161</t>
+          <t>003006</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -32860,12 +32860,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -32875,7 +32875,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>002162</t>
+          <t>300183</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -32892,12 +32892,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -32907,7 +32907,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>002166</t>
+          <t>300369</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -32924,12 +32924,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>002172</t>
+          <t>300411</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -32956,12 +32956,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -32971,7 +32971,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>002187</t>
+          <t>300427</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -32988,12 +32988,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -33003,7 +33003,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>002204</t>
+          <t>300741</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -33020,12 +33020,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -33035,7 +33035,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>002209</t>
+          <t>301006</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -33052,12 +33052,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -33067,7 +33067,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>002246</t>
+          <t>301357</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -33084,12 +33084,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -33099,7 +33099,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>002295</t>
+          <t>600016</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -33116,12 +33116,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>002320</t>
+          <t>600088</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -33148,12 +33148,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -33163,7 +33163,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>002343</t>
+          <t>600104</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -33180,12 +33180,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -33195,7 +33195,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>002349</t>
+          <t>600108</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -33212,12 +33212,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>002377</t>
+          <t>600163</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -33244,12 +33244,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -33259,7 +33259,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>002389</t>
+          <t>600177</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -33276,12 +33276,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -33291,7 +33291,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>002403</t>
+          <t>600192</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -33308,12 +33308,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -33323,7 +33323,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>002408</t>
+          <t>600310</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -33340,12 +33340,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -33355,7 +33355,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>002451</t>
+          <t>600354</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -33372,12 +33372,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -33387,7 +33387,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>002470</t>
+          <t>600359</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -33404,12 +33404,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -33419,7 +33419,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>002481</t>
+          <t>600371</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -33436,12 +33436,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -33451,7 +33451,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>002493</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -33468,12 +33468,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -33483,7 +33483,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>002561</t>
+          <t>600682</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -33500,12 +33500,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -33515,7 +33515,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>002579</t>
+          <t>600706</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -33532,12 +33532,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -33547,7 +33547,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>002596</t>
+          <t>600710</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -33564,12 +33564,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -33579,7 +33579,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>002616</t>
+          <t>600712</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -33596,12 +33596,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>002651</t>
+          <t>600792</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -33628,12 +33628,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -33643,7 +33643,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>002652</t>
+          <t>600865</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -33660,12 +33660,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -33675,7 +33675,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>002661</t>
+          <t>600876</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -33692,12 +33692,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -33707,7 +33707,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>002692</t>
+          <t>600919</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -33724,12 +33724,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -33739,7 +33739,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>002702</t>
+          <t>600938</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -33756,12 +33756,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -33771,7 +33771,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>002790</t>
+          <t>601009</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -33788,12 +33788,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -33803,7 +33803,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>002807</t>
+          <t>601086</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -33820,12 +33820,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -33835,7 +33835,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>002909</t>
+          <t>601330</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -33852,12 +33852,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>002911</t>
+          <t>601595</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -33884,12 +33884,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>002913</t>
+          <t>601838</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -33916,12 +33916,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -33931,7 +33931,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>002966</t>
+          <t>601949</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -33948,12 +33948,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -33963,7 +33963,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>002980</t>
+          <t>603042</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -33980,12 +33980,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -33995,7 +33995,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>003006</t>
+          <t>603105</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -34012,12 +34012,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -34027,7 +34027,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>003029</t>
+          <t>603136</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -34044,12 +34044,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -34059,7 +34059,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>300008</t>
+          <t>603268</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -34076,12 +34076,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -34091,7 +34091,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>300013</t>
+          <t>603421</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -34108,12 +34108,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>300021</t>
+          <t>603657</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -34140,12 +34140,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -34155,7 +34155,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>300050</t>
+          <t>603938</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -34172,12 +34172,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -34187,7 +34187,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>300135</t>
+          <t>605077</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -34204,12 +34204,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -34219,7 +34219,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>300154</t>
+          <t>605177</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -34236,12 +34236,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -34251,7 +34251,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>300332</t>
+          <t>688023</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -34268,12 +34268,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -34283,7 +34283,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>300335</t>
+          <t>688151</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -34300,12 +34300,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -34315,7 +34315,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>300483</t>
+          <t>688543</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -34332,12 +34332,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>300589</t>
+          <t>688581</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -34364,12 +34364,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -34379,7 +34379,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>300600</t>
+          <t>688655</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -34396,12 +34396,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -34411,7 +34411,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>300673</t>
+          <t>920008</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -34428,12 +34428,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-10 19:45:40+0800</t>
+          <t>2026-09-11 15:51:44+0800</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -34443,7 +34443,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>300741</t>
+          <t>920821</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -34452,3782 +34452,6 @@
         </is>
       </c>
       <c r="F205" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>300788</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>300810</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>300951</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>301016</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>301046</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>301085</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>301223</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>301251</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>301282</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>301505</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>600017</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>600075</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>600104</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>600108</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>600121</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>600138</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>600150</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>600177</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>600192</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>600249</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>600256</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>600279</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>600303</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>600307</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>600318</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>600333</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>600336</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>600354</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>600359</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>600371</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>600403</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>600540</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>600681</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>600685</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>600704</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>600706</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>600710</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>600712</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>600731</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>600758</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>600764</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>600778</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>600792</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>600794</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>600802</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>600812</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>600822</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>600864</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>600865</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>600871</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>600874</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>600893</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>600903</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>600908</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>600917</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>600919</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>600926</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>600939</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>600989</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>601007</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>601008</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>601009</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>601015</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>601018</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>601022</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>601086</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>601107</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>601128</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>601188</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>601298</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>601326</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>601330</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>601528</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>601577</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>601579</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>601595</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>601665</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>601838</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>601866</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>601890</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>601949</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>601952</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>601969</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>601998</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>603042</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>603069</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>603103</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>603105</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>603136</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>603162</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>603186</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>603209</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>603216</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>603235</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>603268</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>603322</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>603323</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>603366</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>603393</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>603421</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>603518</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>603600</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>603619</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>603679</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>603689</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>603823</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>603900</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>603955</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>603967</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>603991</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>603999</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>605077</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>688215</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>688655</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>688656</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>688660</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>920010</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>第一阶段影子记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:45:40+0800</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>强势股</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>920895</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>eastmoney_public_pool</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
         <is>
           <t>第一阶段影子记录</t>
         </is>
@@ -38244,7 +34468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39387,7 +35611,7 @@
         <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1788321167883212</v>
+        <v>0.1788321167883211</v>
       </c>
       <c r="L7" t="n">
         <v>0.8052247406838263</v>
@@ -39417,7 +35641,7 @@
         <v>48</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1044680929432313</v>
+        <v>-0.1044680929432312</v>
       </c>
       <c r="V7" t="n">
         <v>0.4583333333333333</v>
@@ -39509,6 +35733,171 @@
         <v>11</v>
       </c>
       <c r="AW7" t="inlineStr">
+        <is>
+          <t>盘后</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:51:44+0800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>legulegu_fallback+eastmoney_public_pool</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>5207</v>
+      </c>
+      <c r="G8" t="n">
+        <v>604</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4567</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.115997695410025</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8770885346648742</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-3963</v>
+      </c>
+      <c r="N8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O8" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>58</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>35</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.5672386062996729</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.775486893124051</v>
+      </c>
+      <c r="X8" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>000636|000823|000980|000993|001232|002161|002201|002218|002242|002519|002560|002585|002790|002815|002848|002902|002912|300563|600088|600184|600207|600237|600410|600876|600967|601199|603136|603336|603386|603421|603439|603466|603693|603936|603938|605011|605058|605069|605088|605258</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>000017|000428|000523|000737|002040|002059|002162|002295|002403|002661|002702|002855|002909|600108|600318|600479|600540|600865|601949|603123|603366</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>000070|000679|000722|000759|000890|000978|002194|002297|003013|600255|600359|600371|600706|600712|600792|603226|603328|603601</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>000048|000532|000565|000722|000823|000978|000993|001299|002174|002201|002204|002377|002531|002543|002636|002661|002790|002912|600192|600318|600359|600488|600644|600667|600712|600744|600792|600876|601231|603105|603316|603318|603421|603601|920268</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>000523|000565|000722|000759|000798|000823|000839|000912|000921|000930|000978|000980|000993|001234|002011|002068|002161|002174|002201|002242|002265|002295|002316|002349|002377|002389|002403|002443|002470|002508|002652|002702|002790|002848|002909|002912|002913|002966|002998|003006|300183|300369|300411|300427|300741|301006|301357|600016|600088|600104|600108|600163|600177|600192|600310|600354|600359|600371|600540|600682|600706|600710|600712|600792|600865|600876|600919|600938|601009|601086|601330|601595|601838|601949|603042|603105|603136|603268|603421|603657|603938|605077|605177|688023|688151|688543|688581|688655|920008|920821</t>
+        </is>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:00:00</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>604</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>4567</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>上涨/下跌/平盘由逐股快照计数；涨停/跌停读取东方财富公开池；炸板、封板率、昨日涨停溢价、连板高度为影子情绪层，仅记录和QA，暂不改变推荐。乐咕只做交叉核验。</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW8" t="inlineStr">
         <is>
           <t>盘后</t>
         </is>
@@ -39793,11 +36182,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -39805,124 +36194,124 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1788321167883212</v>
+        <v>0.115997695410025</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1438877968652136</v>
+        <v>-0.06283442137829612</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4071646281887403</v>
+        <v>0.3632174525992782</v>
       </c>
       <c r="G2" t="n">
         <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3946693591646057</v>
+        <v>0.3548591214853798</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3946693591646057</v>
+        <v>0.3548591214853798</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8052247406838263</v>
+        <v>0.8770885346648742</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1502508245118529</v>
+        <v>0.07186379398104792</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5668216783602542</v>
+        <v>0.6166588272374235</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5794813950325369</v>
+        <v>0.6219967006942994</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5794813950325369</v>
+        <v>0.6219967006942994</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>-3261</v>
+        <v>-3963</v>
       </c>
       <c r="U2" t="n">
-        <v>-1414</v>
+        <v>-702</v>
       </c>
       <c r="V2" t="n">
-        <v>-857.4</v>
+        <v>-1325.4</v>
       </c>
       <c r="W2" t="n">
         <v>0.2</v>
       </c>
       <c r="X2" t="n">
-        <v>-1002</v>
+        <v>-1425</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1002</v>
+        <v>-1425</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AB2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AC2" t="n">
-        <v>-13</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
         <v>58</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>55.66666666666666</v>
+        <v>53.42857142857143</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AH2" t="n">
-        <v>55.66666666666666</v>
+        <v>53.42857142857143</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AM2" t="n">
         <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.833333333333333</v>
+        <v>9.714285714285714</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.833333333333333</v>
+        <v>9.714285714285714</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>1872759350176</v>
@@ -40168,7 +36557,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F8" t="inlineStr"/>
     </row>
@@ -40190,7 +36579,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
@@ -40212,7 +36601,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F10" t="inlineStr"/>
     </row>
@@ -40234,7 +36623,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F11" t="inlineStr"/>
     </row>
@@ -40256,7 +36645,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206</v>
+        <v>90</v>
       </c>
       <c r="F12" t="inlineStr"/>
     </row>
@@ -40308,7 +36697,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>尝试次数=2; 第1次:TimeoutError:upstream call exceeded 45s | 第2次:JSONDecodeError:Can not decode value starting with character '&lt;'</t>
+          <t>尝试次数=2; 第1次:ReadTimeout:HTTPConnectionPool(host='vip.stock.finance.sina.com.cn', port=80): Read timed out. (read timeout=None) | 第2次:ReadTimeout:HTTPConnectionPool(host='vip.stock.finance.sina.com.cn', port=80): Read timed out. (read timeout=None)</t>
         </is>
       </c>
     </row>
@@ -40321,7 +36710,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>警告</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -40332,11 +36721,7 @@
       <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>涨停:正式35/乐咕39 | 跌停:正式11/乐咕14</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
